--- a/Sample_run/1/student/cuongnvhe181200/TC2/GradeDetail.xlsx
+++ b/Sample_run/1/student/cuongnvhe181200/TC2/GradeDetail.xlsx
@@ -158,9 +158,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PASS</x:t>
   </x:si>
   <x:si>
@@ -188,10 +185,10 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -921,7 +918,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R11"/>
+  <x:dimension ref="A1:R7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -935,7 +932,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1035,7 +1032,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
         <x:v>44</x:v>
@@ -1047,13 +1044,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>45788</x:v>
+        <x:v>38018</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1073,10 +1070,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1088,28 +1085,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1129,10 +1126,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1144,36 +1141,36 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R4" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
       <x:c r="A5" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>17</x:v>
@@ -1203,7 +1200,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
         <x:v>44</x:v>
@@ -1215,21 +1212,21 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35790</x:v>
+        <x:v>35924</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
       <x:c r="A6" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>17</x:v>
@@ -1256,10 +1253,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>45</x:v>
@@ -1274,290 +1271,66 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35790</x:v>
+        <x:v>35924</x:v>
       </x:c>
       <x:c r="R6" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
       <x:c r="A7" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q7" s="0">
+        <x:v>38018</x:v>
+      </x:c>
+      <x:c r="R7" s="4" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K7" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L7" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M7" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N7" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O7" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P7" s="0">
-        <x:v>35828</x:v>
-      </x:c>
-      <x:c r="Q7" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:18">
-      <x:c r="A8" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K8" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q8" s="0">
-        <x:v>35828</x:v>
-      </x:c>
-      <x:c r="R8" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:18">
-      <x:c r="A9" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="0">
-        <x:v>53646</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R9" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:18">
-      <x:c r="A10" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>53646</x:v>
-      </x:c>
-      <x:c r="R10" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:18">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>45788</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
-        <x:v>55</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Sample_run/1/student/cuongnvhe181200/TC2/GradeDetail.xlsx
+++ b/Sample_run/1/student/cuongnvhe181200/TC2/GradeDetail.xlsx
@@ -1044,7 +1044,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>38018</x:v>
+        <x:v>54516</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1212,7 +1212,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35924</x:v>
+        <x:v>54478</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35924</x:v>
+        <x:v>54478</x:v>
       </x:c>
       <x:c r="R6" s="4" t="s">
         <x:v>54</x:v>
@@ -1327,7 +1327,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>38018</x:v>
+        <x:v>54516</x:v>
       </x:c>
       <x:c r="R7" s="4" t="s">
         <x:v>54</x:v>
